--- a/excel-files/PASAY/P. VILLANUEVA ELEMENTARY SCHOOL.xlsx
+++ b/excel-files/PASAY/P. VILLANUEVA ELEMENTARY SCHOOL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29816"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29825"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonathan Buquia\Downloads\OFFICE\SEMINARS\Workshop on the Strengthened Regional Inventory of Learning Resources\SCHOOLS in NCR\CALOOCAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="204" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9E4CB5C7-6762-4272-96C2-648653C6E5DA}"/>
+  <xr:revisionPtr revIDLastSave="207" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A6697D4E-5868-4A21-B1EA-C64CBC1F66BF}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TextBooks" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="406" uniqueCount="93">
   <si>
     <t>Grade Level</t>
   </si>
@@ -4122,16 +4122,22 @@
       <c r="C29" s="1">
         <v>123</v>
       </c>
-      <c r="D29" s="1"/>
-      <c r="E29" s="1"/>
-      <c r="F29" s="5"/>
+      <c r="D29" s="1">
+        <v>168</v>
+      </c>
+      <c r="E29" s="1">
+        <v>2026</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>16</v>
+      </c>
       <c r="G29" s="3">
         <f t="shared" si="4"/>
-        <v>123</v>
+        <v>0</v>
       </c>
       <c r="H29" s="4">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>45</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="27.75" customHeight="1">
@@ -13898,7 +13904,7 @@
     <mergeCell ref="P1:U1"/>
     <mergeCell ref="V1:AA1"/>
   </mergeCells>
-  <dataValidations count="5">
+  <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S112:S127 M112:M127 Y112:Y127 G112:G127" xr:uid="{8289B4A9-982E-4C7E-A8E2-4BF3404561DB}">
       <formula1>"CO,RO,SDO"</formula1>
     </dataValidation>
@@ -13908,10 +13914,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M14:M110 Y14:Y110 S4:S110 G5:G12 M5:M12 Y5:Y12 G14:G21 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G103:G110" xr:uid="{5129D80C-83DF-45BE-B6AD-F21CA596CBA5}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F5:F12 F14:F21 F23:F31 F33:F41 F43:F51 F53:F61" xr:uid="{EE735B69-1FBC-4002-A4A6-9E70C9234C3F}">
-      <formula1>"2024,2025,2026"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X3 X5:X12 X14:X21 X23:X31 X33:X41 X43:X51 X53:X61 R5:R12 R14:R21 R23:R31 R33:R41 R43:R51 R53:R61 L5:L12 L14:L21 L23:L31 L33:L41 L43:L51 L53:L61" xr:uid="{AC64BE6A-9836-455B-AE7F-98D2E94499DE}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F5:F12 F14:F21 F23:F31 F33:F41 F43:F51 F53:F61 X3 X5:X12 X14:X21 X23:X31 X33:X41 X43:X51 X53:X61 R5:R12 R14:R21 R23:R31 R33:R41 R43:R51 R53:R61 L5:L12 L14:L21 L23:L31 L33:L41 L43:L51 L53:L61" xr:uid="{EE735B69-1FBC-4002-A4A6-9E70C9234C3F}">
       <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
